--- a/exports/BAJAJ-AUTO_full_report.xlsx
+++ b/exports/BAJAJ-AUTO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.05</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>3367</v>
+        <v>3235.5</v>
       </c>
       <c r="I2" t="n">
         <v>3299.798845858204</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0.39</v>
+        <v>-3.53</v>
       </c>
       <c r="L2" t="n">
-        <v>1.61</v>
+        <v>3.95</v>
       </c>
       <c r="M2" t="n">
-        <v>0.67</v>
+        <v>1.54</v>
       </c>
       <c r="N2" t="n">
-        <v>2.04</v>
+        <v>4.14</v>
       </c>
       <c r="O2" t="n">
         <v>1.21</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>6.95</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.38541666666</v>
+        <v>44588.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>3358</v>
+        <v>3418.5</v>
       </c>
       <c r="I3" t="n">
         <v>3386.57359705827</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.79</v>
+        <v>-5.66</v>
       </c>
       <c r="L3" t="n">
-        <v>5.19</v>
+        <v>6.57</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.91</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>3416</v>
+        <v>3350</v>
       </c>
       <c r="I4" t="n">
         <v>3367.142120933046</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27.83333333333333</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>2.92</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.63</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44630.38541666666</v>
+        <v>44630.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>3324.5</v>
+        <v>3335.5</v>
       </c>
       <c r="I5" t="n">
         <v>3334.153891890759</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
       <c r="L5" t="n">
         <v>3.67</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.83</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>3616.5</v>
+        <v>3545.5</v>
       </c>
       <c r="I6" t="n">
         <v>3567.813195758645</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39.83333333333334</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>8.42</v>
+        <v>6.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.51</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44677.38541666666</v>
+        <v>44677.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>3708</v>
+        <v>3808.5</v>
       </c>
       <c r="I7" t="n">
         <v>3734.967346435869</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.58</v>
+        <v>-7.42</v>
       </c>
       <c r="L7" t="n">
-        <v>5.89</v>
+        <v>7.42</v>
       </c>
       <c r="M7" t="n">
         <v>0.85</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>7.16</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44680.55208333334</v>
+        <v>44683.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>3642.5</v>
+        <v>3529.5</v>
       </c>
       <c r="I8" t="n">
         <v>3592.489639442775</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.36</v>
+        <v>-7.33</v>
       </c>
       <c r="L8" t="n">
-        <v>4.96</v>
+        <v>7.65</v>
       </c>
       <c r="M8" t="n">
         <v>0.89</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>3.02</v>
       </c>
       <c r="O8" t="n">
         <v>5.05</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.01</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>3612.5</v>
+        <v>3687.5</v>
       </c>
       <c r="I9" t="n">
         <v>3636.084572609488</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.35</v>
+        <v>-4.48</v>
       </c>
       <c r="L9" t="n">
-        <v>3.22</v>
+        <v>4.56</v>
       </c>
       <c r="M9" t="n">
         <v>1.17</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.84</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44713.55208333334</v>
+        <v>44714.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>3631</v>
+        <v>3596</v>
       </c>
       <c r="I10" t="n">
         <v>3625.541879633863</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.53</v>
+        <v>-2.48</v>
       </c>
       <c r="L10" t="n">
         <v>2.67</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>6.64</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44721.38541666666</v>
+        <v>44721.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>3741.5</v>
+        <v>3779</v>
       </c>
       <c r="I11" t="n">
         <v>3772.34353197595</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.05</v>
+        <v>-5.09</v>
       </c>
       <c r="L11" t="n">
-        <v>4.89</v>
+        <v>5.63</v>
       </c>
       <c r="M11" t="n">
         <v>0.78</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.66</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44726.55208333334</v>
+        <v>44727.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3602.5</v>
+        <v>3594.5</v>
       </c>
       <c r="I12" t="n">
         <v>3595.88519564964</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.67</v>
+        <v>-4.88</v>
       </c>
       <c r="L12" t="n">
         <v>7.01</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.59</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>3730</v>
+        <v>3801.5</v>
       </c>
       <c r="I13" t="n">
         <v>3735.661795780818</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.77</v>
+        <v>-5.76</v>
       </c>
       <c r="L13" t="n">
-        <v>4.23</v>
+        <v>6.09</v>
       </c>
       <c r="M13" t="n">
         <v>1.32</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.08</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44742.55208333334</v>
+        <v>44743.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3609.5</v>
+        <v>3530.5</v>
       </c>
       <c r="I14" t="n">
         <v>3573.034427198109</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.05</v>
+        <v>-7.13</v>
       </c>
       <c r="L14" t="n">
-        <v>5.29</v>
+        <v>7.62</v>
       </c>
       <c r="M14" t="n">
         <v>3.22</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.99</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44750.55208333334</v>
+        <v>44753.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3730.5</v>
+        <v>3741</v>
       </c>
       <c r="I15" t="n">
         <v>3737.834037315321</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.66</v>
+        <v>-5.96</v>
       </c>
       <c r="L15" t="n">
-        <v>5.98</v>
+        <v>6.57</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>4.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44768.55208333334</v>
+        <v>44769.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3835</v>
+        <v>3766.5</v>
       </c>
       <c r="I16" t="n">
         <v>3834.970738308395</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>2.51</v>
+        <v>0.68</v>
       </c>
       <c r="L16" t="n">
         <v>1.07</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.71</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44783.38541666666</v>
+        <v>44783.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>3921.5</v>
+        <v>3930.5</v>
       </c>
       <c r="I17" t="n">
         <v>3927.084741098621</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.12</v>
+        <v>-4.35</v>
       </c>
       <c r="L17" t="n">
         <v>5.28</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>3.09</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44806.55208333334</v>
+        <v>44809.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>3938</v>
+        <v>3869</v>
       </c>
       <c r="I18" t="n">
         <v>3886.606287811787</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>0.19</v>
+        <v>-1.56</v>
       </c>
       <c r="L18" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="M18" t="n">
         <v>2.03</v>
       </c>
       <c r="N18" t="n">
-        <v>0.93</v>
+        <v>1.88</v>
       </c>
       <c r="O18" t="n">
         <v>0.2</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.01</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44852.55208333334</v>
+        <v>44853.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>3532</v>
+        <v>3573</v>
       </c>
       <c r="I19" t="n">
         <v>3556.286770225134</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K19" t="n">
-        <v>8.710000000000001</v>
+        <v>7.65</v>
       </c>
       <c r="L19" t="n">
         <v>2.24</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.56</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44883.38541666666</v>
+        <v>44883.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>3568</v>
+        <v>3538</v>
       </c>
       <c r="I20" t="n">
         <v>3561.876378885553</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.14</v>
+        <v>-0.98</v>
       </c>
       <c r="L20" t="n">
         <v>2.11</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>3.99</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44894.55208333334</v>
+        <v>44895.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3564.5</v>
+        <v>3657.5</v>
       </c>
       <c r="I21" t="n">
         <v>3637.052774100741</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.75</v>
+        <v>-3.38</v>
       </c>
       <c r="L21" t="n">
-        <v>2.28</v>
+        <v>3.5</v>
       </c>
       <c r="M21" t="n">
         <v>0.71</v>
       </c>
       <c r="N21" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="O21" t="n">
         <v>-1.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>4.39</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3552</v>
+        <v>3525.5</v>
       </c>
       <c r="I22" t="n">
         <v>3534.551281541951</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.88</v>
+        <v>-3.61</v>
       </c>
       <c r="L22" t="n">
         <v>4.05</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.14</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>3566.5</v>
+        <v>3593</v>
       </c>
       <c r="I23" t="n">
         <v>3575.487976178245</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.16</v>
+        <v>-1.91</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>2.24</v>
       </c>
       <c r="M23" t="n">
         <v>0.59</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3739.5</v>
+        <v>3558.5</v>
       </c>
       <c r="I24" t="n">
         <v>3694.472353727056</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>4.08</v>
+        <v>-0.96</v>
       </c>
       <c r="L24" t="n">
-        <v>0.95</v>
+        <v>1.29</v>
       </c>
       <c r="M24" t="n">
-        <v>0.43</v>
+        <v>0.9</v>
       </c>
       <c r="N24" t="n">
-        <v>2.51</v>
+        <v>4.93</v>
       </c>
       <c r="O24" t="n">
         <v>1.57</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>6.63</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44993.55208333334</v>
+        <v>44994.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>3711</v>
+        <v>3728.5</v>
       </c>
       <c r="I25" t="n">
         <v>3714.334600069958</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.29</v>
+        <v>-4.78</v>
       </c>
       <c r="L25" t="n">
-        <v>4.61</v>
+        <v>5.21</v>
       </c>
       <c r="M25" t="n">
         <v>0.65</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45092.55208333334</v>
+        <v>45093.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>4597</v>
+        <v>4516</v>
       </c>
       <c r="I26" t="n">
         <v>4566.913184898702</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>98.16666666666667</v>
+        <v>99</v>
       </c>
       <c r="K26" t="n">
-        <v>23.29</v>
+        <v>21.12</v>
       </c>
       <c r="L26" t="n">
         <v>2.68</v>
@@ -1923,7 +2234,7 @@
         <v>0.83</v>
       </c>
       <c r="N26" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O26" t="n">
         <v>0.03</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>3.71</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45105.38541666666</v>
+        <v>45105.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>4512.5</v>
+        <v>4608</v>
       </c>
       <c r="I27" t="n">
         <v>4603.517157509521</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>0.08</v>
+        <v>-2.04</v>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="M27" t="n">
         <v>0.66</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.02</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45141.55208333334</v>
+        <v>45142.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>4702</v>
+        <v>4631.5</v>
       </c>
       <c r="I28" t="n">
         <v>4650.356892472968</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K28" t="n">
-        <v>2.04</v>
+        <v>0.51</v>
       </c>
       <c r="L28" t="n">
         <v>2.9</v>
@@ -2037,7 +2372,7 @@
         <v>1.88</v>
       </c>
       <c r="N28" t="n">
-        <v>1.99</v>
+        <v>2.44</v>
       </c>
       <c r="O28" t="n">
         <v>2.29</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.2</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45176.55208333334</v>
+        <v>45177.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>4598.5</v>
+        <v>4642</v>
       </c>
       <c r="I29" t="n">
         <v>4615.502798500491</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K29" t="n">
-        <v>0.71</v>
+        <v>-0.23</v>
       </c>
       <c r="L29" t="n">
         <v>2.43</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.83</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>4885</v>
+        <v>4805</v>
       </c>
       <c r="I30" t="n">
         <v>4857.250972104068</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K30" t="n">
-        <v>5.23</v>
+        <v>3.51</v>
       </c>
       <c r="L30" t="n">
         <v>1.2</v>
@@ -2151,7 +2510,7 @@
         <v>0.66</v>
       </c>
       <c r="N30" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0.85</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>4.81</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45210.55208333334</v>
+        <v>45211.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>4941.5</v>
+        <v>5002.5</v>
       </c>
       <c r="I31" t="n">
         <v>4981.07203082372</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.84</v>
+        <v>-4.11</v>
       </c>
       <c r="L31" t="n">
-        <v>3.92</v>
+        <v>4.55</v>
       </c>
       <c r="M31" t="n">
         <v>1.9</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.24</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45225.38541666666</v>
+        <v>45225.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>5159.5</v>
+        <v>5125.5</v>
       </c>
       <c r="I32" t="n">
         <v>5133.819195873657</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>3.14</v>
+        <v>2.46</v>
       </c>
       <c r="L32" t="n">
         <v>1.9</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,25 +2696,25 @@
         <v>3.97</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>5278</v>
+        <v>5386.5</v>
       </c>
       <c r="I33" t="n">
         <v>5329.081306475708</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.98</v>
+        <v>-5.09</v>
       </c>
       <c r="L33" t="n">
-        <v>3.79</v>
+        <v>5.7</v>
       </c>
       <c r="M33" t="n">
-        <v>0.93</v>
+        <v>2.09</v>
       </c>
       <c r="N33" t="n">
         <v>2.68</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>3.69</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45350.55208333334</v>
+        <v>45351.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>7939</v>
+        <v>7754</v>
       </c>
       <c r="I34" t="n">
         <v>7896.732824741265</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>105.1666666666667</v>
+        <v>106</v>
       </c>
       <c r="K34" t="n">
-        <v>47.39</v>
+        <v>43.95</v>
       </c>
       <c r="L34" t="n">
         <v>1.12</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>6.87</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>8143.5</v>
+        <v>8304.5</v>
       </c>
       <c r="I35" t="n">
         <v>8157.313737681507</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.02</v>
+        <v>-7.1</v>
       </c>
       <c r="L35" t="n">
-        <v>5.5</v>
+        <v>7.15</v>
       </c>
       <c r="M35" t="n">
         <v>0.36</v>
       </c>
       <c r="N35" t="n">
-        <v>1.93</v>
+        <v>3.41</v>
       </c>
       <c r="O35" t="n">
         <v>-2.63</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>5.89</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>8208</v>
+        <v>8143.5</v>
       </c>
       <c r="I36" t="n">
         <v>8183.439986829013</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.16</v>
+        <v>-1.94</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="M36" t="n">
         <v>0.2</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.46</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45372.55208333334</v>
+        <v>45373.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>8531</v>
+        <v>8762</v>
       </c>
       <c r="I37" t="n">
         <v>8606.309157359301</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.76</v>
+        <v>-7.6</v>
       </c>
       <c r="L37" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="O37" t="n">
         <v>-2.03</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.38</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45406.38541666666</v>
+        <v>45406.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>8558</v>
+        <v>8479</v>
       </c>
       <c r="I38" t="n">
         <v>8539.40501977221</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.33</v>
+        <v>-3.23</v>
       </c>
       <c r="L38" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="M38" t="n">
         <v>0.65</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>5.17</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45414.55208333334</v>
+        <v>45415.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>8861.5</v>
+        <v>8924</v>
       </c>
       <c r="I39" t="n">
         <v>8876.7849872523</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.51</v>
+        <v>-5.25</v>
       </c>
       <c r="L39" t="n">
-        <v>5.21</v>
+        <v>6.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0.44</v>
+        <v>0.93</v>
       </c>
       <c r="N39" t="n">
         <v>2.56</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.36</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>8831</v>
+        <v>8480</v>
       </c>
       <c r="I40" t="n">
         <v>8535.237837326355</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.04</v>
+        <v>-4.98</v>
       </c>
       <c r="L40" t="n">
-        <v>3.71</v>
+        <v>5.12</v>
       </c>
       <c r="M40" t="n">
         <v>-0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.33</v>
+        <v>3.93</v>
       </c>
       <c r="O40" t="n">
         <v>-0.01</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.27</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>8875</v>
+        <v>9159</v>
       </c>
       <c r="I41" t="n">
         <v>8921.438898629654</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.66</v>
+        <v>-8.01</v>
       </c>
       <c r="L41" t="n">
-        <v>5.11</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M41" t="n">
         <v>1.25</v>
       </c>
       <c r="N41" t="n">
-        <v>1.75</v>
+        <v>2.54</v>
       </c>
       <c r="O41" t="n">
         <v>-3.93</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.71</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45468.55208333334</v>
+        <v>45469.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>9411.5</v>
+        <v>9245.5</v>
       </c>
       <c r="I42" t="n">
         <v>9331.171627034259</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K42" t="n">
-        <v>2.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>6.21</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.05</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>9483.5</v>
+        <v>9556</v>
       </c>
       <c r="I43" t="n">
         <v>9518.501071115785</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>51</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.57</v>
+        <v>-3.36</v>
       </c>
       <c r="L43" t="n">
         <v>4.54</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>3.94</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>12049.5</v>
+        <v>11859.5</v>
       </c>
       <c r="I44" t="n">
         <v>11915.17527195578</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K44" t="n">
-        <v>26.09</v>
+        <v>24.11</v>
       </c>
       <c r="L44" t="n">
         <v>1.06</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.96</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45659.38541666666</v>
+        <v>45659.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>8684</v>
+        <v>8838</v>
       </c>
       <c r="I45" t="n">
         <v>8831.424425968586</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>93</v>
+        <v>93.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>26.78</v>
+        <v>25.48</v>
       </c>
       <c r="L45" t="n">
         <v>2.8</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>5.67</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>8407</v>
+        <v>8363</v>
       </c>
       <c r="I46" t="n">
         <v>8367.992234122012</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.88</v>
+        <v>-5.37</v>
       </c>
       <c r="L46" t="n">
-        <v>5.64</v>
+        <v>5.92</v>
       </c>
       <c r="M46" t="n">
         <v>0.8</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.33</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45685.55208333334</v>
+        <v>45686.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>8211.5</v>
+        <v>8486</v>
       </c>
       <c r="I47" t="n">
         <v>8458.057288876989</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>1.81</v>
+        <v>-1.47</v>
       </c>
       <c r="L47" t="n">
-        <v>2.61</v>
+        <v>2.71</v>
       </c>
       <c r="M47" t="n">
         <v>0.65</v>
       </c>
       <c r="N47" t="n">
-        <v>0.28</v>
+        <v>2.65</v>
       </c>
       <c r="O47" t="n">
         <v>-0.02</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.46</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>8451.5</v>
+        <v>8298</v>
       </c>
       <c r="I48" t="n">
         <v>8411.373230716101</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.41</v>
+        <v>-2.22</v>
       </c>
       <c r="L48" t="n">
         <v>3.23</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.95</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>7520.5</v>
+        <v>7746.5</v>
       </c>
       <c r="I49" t="n">
         <v>7598.558316435896</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K49" t="n">
-        <v>9.369999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="L49" t="n">
         <v>2.52</v>
@@ -3234,7 +3821,7 @@
         <v>0.65</v>
       </c>
       <c r="N49" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="O49" t="n">
         <v>-2.32</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.91</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>7714</v>
+        <v>7500</v>
       </c>
       <c r="I50" t="n">
         <v>7598.663123496992</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.42</v>
+        <v>-3.18</v>
       </c>
       <c r="L50" t="n">
         <v>3.92</v>
@@ -3291,7 +3890,7 @@
         <v>2.91</v>
       </c>
       <c r="N50" t="n">
-        <v>1.6</v>
+        <v>2.65</v>
       </c>
       <c r="O50" t="n">
         <v>2.59</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.81</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45758.38541666666</v>
+        <v>45758.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>7565.5</v>
+        <v>7586.5</v>
       </c>
       <c r="I51" t="n">
         <v>7586.269377583289</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.87</v>
+        <v>-1.15</v>
       </c>
       <c r="L51" t="n">
         <v>2.6</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.12</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>7817</v>
+        <v>7644.5</v>
       </c>
       <c r="I52" t="n">
         <v>7664.477764896881</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>19</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>3.04</v>
+        <v>0.76</v>
       </c>
       <c r="L52" t="n">
         <v>0.82</v>
@@ -3405,7 +4028,7 @@
         <v>0.54</v>
       </c>
       <c r="N52" t="n">
-        <v>2.49</v>
+        <v>2.57</v>
       </c>
       <c r="O52" t="n">
         <v>2.67</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.43</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>7802.5</v>
+        <v>7848</v>
       </c>
       <c r="I53" t="n">
         <v>7825.131011329607</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.07</v>
+        <v>-2.66</v>
       </c>
       <c r="L53" t="n">
         <v>3.16</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>4.8</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>8386.5</v>
+        <v>8276</v>
       </c>
       <c r="I54" t="n">
         <v>8377.120851987554</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>6.86</v>
+        <v>5.45</v>
       </c>
       <c r="L54" t="n">
         <v>1.2</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.48</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>8321.5</v>
+        <v>8335.5</v>
       </c>
       <c r="I55" t="n">
         <v>8330.143155336256</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.55</v>
+        <v>-0.72</v>
       </c>
       <c r="L55" t="n">
         <v>3.35</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>3.09</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>8288</v>
+        <v>8099.5</v>
       </c>
       <c r="I56" t="n">
         <v>8181.854982504912</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.57</v>
+        <v>-2.83</v>
       </c>
       <c r="L56" t="n">
-        <v>0.71</v>
+        <v>3.49</v>
       </c>
       <c r="M56" t="n">
         <v>0.4</v>
       </c>
       <c r="N56" t="n">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="O56" t="n">
         <v>0.21</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.54</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>8210.5</v>
+        <v>8577.5</v>
       </c>
       <c r="I57" t="n">
         <v>8272.920146490647</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.37</v>
+        <v>-5.9</v>
       </c>
       <c r="L57" t="n">
-        <v>2.74</v>
+        <v>6.54</v>
       </c>
       <c r="M57" t="n">
-        <v>0.58</v>
+        <v>2.31</v>
       </c>
       <c r="N57" t="n">
-        <v>1.58</v>
+        <v>4.65</v>
       </c>
       <c r="O57" t="n">
         <v>-2.58</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.3</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>9025</v>
+        <v>9000</v>
       </c>
       <c r="I58" t="n">
         <v>9000.76912291695</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K58" t="n">
-        <v>5.22</v>
+        <v>4.93</v>
       </c>
       <c r="L58" t="n">
         <v>2.07</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.79</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45940.55208333334</v>
+        <v>45943.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>8943</v>
+        <v>9047</v>
       </c>
       <c r="I59" t="n">
         <v>8949.916741688154</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>0.63</v>
+        <v>-0.52</v>
       </c>
       <c r="L59" t="n">
         <v>2.5</v>
@@ -3804,7 +4511,7 @@
         <v>0.51</v>
       </c>
       <c r="N59" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="O59" t="n">
         <v>0.06</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>4.11</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45960.55208333334</v>
+        <v>45961.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>8914</v>
+        <v>8885</v>
       </c>
       <c r="I60" t="n">
         <v>8896.99044119893</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.47</v>
+        <v>-1.79</v>
       </c>
       <c r="L60" t="n">
-        <v>1.58</v>
+        <v>2.71</v>
       </c>
       <c r="M60" t="n">
         <v>0.03</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>3.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45975.55208333334</v>
+        <v>45978.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>8853.5</v>
+        <v>8985.5</v>
       </c>
       <c r="I61" t="n">
         <v>8958.27625128705</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K61" t="n">
-        <v>0.35</v>
+        <v>-1.13</v>
       </c>
       <c r="L61" t="n">
         <v>1.87</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.64</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46008.38541666666</v>
+        <v>46008.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>8922</v>
+        <v>8868</v>
       </c>
       <c r="I62" t="n">
         <v>8885.08841689817</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.71</v>
+        <v>-1.31</v>
       </c>
       <c r="L62" t="n">
         <v>1.51</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>3.35</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>9000</v>
+        <v>9127</v>
       </c>
       <c r="I63" t="n">
         <v>9086.385737242932</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.49</v>
+        <v>-2.92</v>
       </c>
       <c r="L63" t="n">
-        <v>1.61</v>
+        <v>3.24</v>
       </c>
       <c r="M63" t="n">
         <v>0.26</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>3.88</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>9415</v>
+        <v>9265</v>
       </c>
       <c r="I64" t="n">
         <v>9403.144374296058</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K64" t="n">
-        <v>3.16</v>
+        <v>1.51</v>
       </c>
       <c r="L64" t="n">
         <v>1.42</v>
@@ -4089,7 +4856,7 @@
         <v>0.33</v>
       </c>
       <c r="N64" t="n">
-        <v>1.84</v>
+        <v>2.53</v>
       </c>
       <c r="O64" t="n">
         <v>1.71</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>5.14</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46052.38541666666</v>
+        <v>46052.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>9536.5</v>
+        <v>9584</v>
       </c>
       <c r="I65" t="n">
         <v>9555.312910872992</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.93</v>
+        <v>-3.44</v>
       </c>
       <c r="L65" t="n">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="M65" t="n">
         <v>0.5600000000000001</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>4.65</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>9955.5</v>
+        <v>9672.5</v>
       </c>
       <c r="I66" t="n">
         <v>9681.568894784505</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>3.88</v>
+        <v>0.92</v>
       </c>
       <c r="L66" t="n">
         <v>4.26</v>
       </c>
       <c r="M66" t="n">
-        <v>0.48</v>
+        <v>2.31</v>
       </c>
       <c r="N66" t="n">
         <v>2.83</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.14</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>9040</v>
+        <v>9382</v>
       </c>
       <c r="I67" t="n">
         <v>9312.950549061405</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K67" t="n">
-        <v>6.54</v>
+        <v>3</v>
       </c>
       <c r="L67" t="n">
         <v>2.78</v>
       </c>
       <c r="M67" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="N67" t="n">
-        <v>2.57</v>
+        <v>3.72</v>
       </c>
       <c r="O67" t="n">
         <v>-1.87</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.53</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>10380</v>
+        <v>10310</v>
       </c>
       <c r="I68" t="n">
         <v>10345.54700067227</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K68" t="n">
-        <v>10.64</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L68" t="n">
         <v>1.28</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>5.44</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>10047</v>
+        <v>10100</v>
       </c>
       <c r="I69" t="n">
         <v>10072.91142723034</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="L69" t="n">
         <v>1.38</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>4.27</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46269.55208333334</v>
+        <v>46272.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>11915</v>
+        <v>11777</v>
       </c>
       <c r="I70" t="n">
         <v>11878.39851487409</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K70" t="n">
-        <v>17.97</v>
+        <v>16.6</v>
       </c>
       <c r="L70" t="n">
         <v>1.06</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>4.2</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>10010</v>
+        <v>10317</v>
       </c>
       <c r="I71" t="n">
         <v>10198.60395193383</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K71" t="n">
-        <v>15</v>
+        <v>12.4</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -4488,7 +5339,7 @@
         <v>0.57</v>
       </c>
       <c r="N71" t="n">
-        <v>1.93</v>
+        <v>3.26</v>
       </c>
       <c r="O71" t="n">
         <v>-0.97</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,14 @@
       <c r="Q72" t="n">
         <v>22</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6650,7 +7521,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="6">
@@ -6660,7 +7531,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="7">
@@ -6670,7 +7541,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105.2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8">
@@ -6680,7 +7551,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6690,7 +7561,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.5</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="10">
@@ -6700,7 +7571,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45.2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
@@ -6710,7 +7581,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -6720,7 +7591,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6730,7 +7601,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6740,7 +7611,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="15">
@@ -6750,7 +7621,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.13</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="16">
@@ -6760,7 +7631,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="17">
@@ -6770,7 +7641,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>47.39</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="18">
@@ -6780,7 +7651,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.3</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="19">
@@ -6790,7 +7661,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.99</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="20">
@@ -6800,7 +7671,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.68</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="21">
@@ -6810,7 +7681,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.01</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -6820,7 +7691,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -6840,7 +7711,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="25">
@@ -6850,7 +7721,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="26">
@@ -6860,7 +7731,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="27">
@@ -6880,7 +7751,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
